--- a/data/trans_orig/P1802_2016_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1802_2016_2023-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107930</t>
+          <t>107633</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147890</t>
+          <t>147165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>206010</t>
+          <t>203536</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>260063</t>
+          <t>259910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322034</t>
+          <t>321985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>390933</t>
+          <t>392970</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>606457</t>
+          <t>607182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>646417</t>
+          <t>646714</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>734597</t>
+          <t>734750</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>788650</t>
+          <t>791124</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1358074</t>
+          <t>1356037</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1426973</t>
+          <t>1427022</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>254516</t>
+          <t>251165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>320635</t>
+          <t>317460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>313347</t>
+          <t>310408</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>382707</t>
+          <t>381529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>580270</t>
+          <t>579598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>671879</t>
+          <t>672906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1755750</t>
+          <t>1758925</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1821869</t>
+          <t>1825220</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1605593</t>
+          <t>1606771</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1674953</t>
+          <t>1677892</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3392806</t>
+          <t>3391779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3484415</t>
+          <t>3485087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>58688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93889</t>
+          <t>93527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>74669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110541</t>
+          <t>111864</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139505</t>
+          <t>140275</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187225</t>
+          <t>189336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452997</t>
+          <t>453359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>487694</t>
+          <t>488198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>438599</t>
+          <t>437276</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>476622</t>
+          <t>474471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>908802</t>
+          <t>906691</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>956522</t>
+          <t>955752</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>440998</t>
+          <t>446321</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>526005</t>
+          <t>527049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>617426</t>
+          <t>620237</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>714229</t>
+          <t>717566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1088057</t>
+          <t>1089302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1214968</t>
+          <t>1218518</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2851613</t>
+          <t>2850569</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2936620</t>
+          <t>2931297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2817871</t>
+          <t>2814534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2914674</t>
+          <t>2911863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5694750</t>
+          <t>5691200</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5821661</t>
+          <t>5820416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,24%</t>
         </is>
       </c>
     </row>
@@ -2329,32 +2329,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>102947</t>
+          <t>106286</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87142</t>
+          <t>91056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>120110</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2364,32 +2364,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>154332</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>136468</t>
+          <t>150878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>169635</t>
+          <t>183208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2399,32 +2399,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>257280</t>
+          <t>272553</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232860</t>
+          <t>248346</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>281500</t>
+          <t>297424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -2442,32 +2442,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>411991</t>
+          <t>472243</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394828</t>
+          <t>452145</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>427796</t>
+          <t>487473</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2477,32 +2477,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>600610</t>
+          <t>655175</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>585307</t>
+          <t>638234</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>618474</t>
+          <t>670564</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1012601</t>
+          <t>1127418</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>988381</t>
+          <t>1102547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1037021</t>
+          <t>1151625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -2555,17 +2555,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>754942</t>
+          <t>821442</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1269881</t>
+          <t>1399971</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2672,32 +2672,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>554093</t>
+          <t>322741</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>335510</t>
+          <t>288735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1128352</t>
+          <t>357407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2707,32 +2707,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>335249</t>
+          <t>381615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256738</t>
+          <t>351224</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>385486</t>
+          <t>414488</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2742,32 +2742,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>889342</t>
+          <t>704356</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>655332</t>
+          <t>654228</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1501422</t>
+          <t>753857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>17,14%</t>
         </is>
       </c>
     </row>
@@ -2785,32 +2785,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1735521</t>
+          <t>1907029</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1161262</t>
+          <t>1872363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1954104</t>
+          <t>1941035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1900598</t>
+          <t>1787736</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1850361</t>
+          <t>1754863</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1979109</t>
+          <t>1818127</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2855,32 +2855,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3636119</t>
+          <t>3694764</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3024039</t>
+          <t>3645263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3870129</t>
+          <t>3744892</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,13%</t>
         </is>
       </c>
     </row>
@@ -2898,17 +2898,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2289614</t>
+          <t>2229770</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2289614</t>
+          <t>2229770</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2289614</t>
+          <t>2229770</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2933,17 +2933,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2235847</t>
+          <t>2169351</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2235847</t>
+          <t>2169351</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2235847</t>
+          <t>2169351</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4525461</t>
+          <t>4399120</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4525461</t>
+          <t>4399120</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4525461</t>
+          <t>4399120</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3015,32 +3015,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>99371</t>
+          <t>105006</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81669</t>
+          <t>86721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120333</t>
+          <t>125589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3050,32 +3050,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138432</t>
+          <t>150627</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121022</t>
+          <t>132871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157625</t>
+          <t>170207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3085,32 +3085,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>237803</t>
+          <t>255634</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213119</t>
+          <t>229061</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264372</t>
+          <t>285500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -3128,32 +3128,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>546505</t>
+          <t>605707</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525543</t>
+          <t>585124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>564207</t>
+          <t>623992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3163,32 +3163,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>521372</t>
+          <t>583567</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>502179</t>
+          <t>563987</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538782</t>
+          <t>601323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3198,32 +3198,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1067878</t>
+          <t>1189273</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1041309</t>
+          <t>1159407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1092562</t>
+          <t>1215846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -3241,17 +3241,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645876</t>
+          <t>710713</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645876</t>
+          <t>710713</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645876</t>
+          <t>710713</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>659804</t>
+          <t>734194</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>659804</t>
+          <t>734194</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>659804</t>
+          <t>734194</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1305681</t>
+          <t>1444907</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1305681</t>
+          <t>1444907</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1305681</t>
+          <t>1444907</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3358,32 +3358,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>756412</t>
+          <t>534034</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>536592</t>
+          <t>492011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1340823</t>
+          <t>578747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3393,32 +3393,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>628013</t>
+          <t>698510</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>526434</t>
+          <t>662408</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>691993</t>
+          <t>739156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3428,32 +3428,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1384425</t>
+          <t>1232543</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1153834</t>
+          <t>1168855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2154015</t>
+          <t>1302175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -3471,32 +3471,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2694017</t>
+          <t>2984978</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2109606</t>
+          <t>2940265</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2913837</t>
+          <t>3027001</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3022580</t>
+          <t>3026477</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2958600</t>
+          <t>2985831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3124159</t>
+          <t>3062579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5716598</t>
+          <t>6011456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4947008</t>
+          <t>5941824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5947189</t>
+          <t>6075144</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -3584,17 +3584,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450429</t>
+          <t>3519012</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450429</t>
+          <t>3519012</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450429</t>
+          <t>3519012</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3619,17 +3619,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3650593</t>
+          <t>3724987</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3650593</t>
+          <t>3724987</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3650593</t>
+          <t>3724987</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3654,17 +3654,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7101023</t>
+          <t>7243999</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7101023</t>
+          <t>7243999</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7101023</t>
+          <t>7243999</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
